--- a/Registros/Plantillas/Tickets/Tickets.xlsx
+++ b/Registros/Plantillas/Tickets/Tickets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69517450a5f14e94/Intranet/Secciones Pendientes y Proyectos/Registros/Plantillas/Tickets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69517450a5f14e94/Intranet/Registros/Plantillas/Tickets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="8_{AB085FBE-04D6-4101-927C-F7B3FED8618B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5887F6D2-7945-489F-9ECA-7922C16A4BA3}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="8_{AB085FBE-04D6-4101-927C-F7B3FED8618B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53D98484-AAED-4B19-970C-A516FE14BC61}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{578E240D-0F4A-4C13-A965-CE407C13011A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="8" xr2:uid="{578E240D-0F4A-4C13-A965-CE407C13011A}"/>
   </bookViews>
   <sheets>
     <sheet name="Activacion" sheetId="8" r:id="rId1"/>
@@ -352,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -388,6 +388,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1116,18 +1120,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="14" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="1" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="15" t="s">
         <v>60</v>
       </c>
     </row>
